--- a/data/out/pricing_comparison.xlsx
+++ b/data/out/pricing_comparison.xlsx
@@ -8,14 +8,16 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SKU Detail" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Offers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Exceptions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Category Expense" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SKU Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Offers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Exceptions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SKU Detail'!$A$1:$W$201</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Offers'!$A$1:$P$578</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Exceptions'!$A$1:$E$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Category Expense'!$A$1:$Q$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SKU Detail'!$A$1:$W$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Offers'!$A$1:$P$578</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Exceptions'!$A$1:$E$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -74,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -86,6 +88,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1161,6 +1166,1151 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>SKUs priced</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Annual units</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Avg unit price</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Annual expense</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Share of expense</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Benchmarked expense</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Unbenchmarked expense</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Benchmark coverage</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>Matched SKUs vs low</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>Index vs market low</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>$ vs market low</t>
+        </is>
+      </c>
+      <c r="N1" s="7" t="inlineStr">
+        <is>
+          <t>Index vs Home Depot</t>
+        </is>
+      </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>$ vs Home Depot</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>Index vs Lowe's</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>$ vs Lowe's</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Luxury Vinyl Plank</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sq_ft</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4228213</v>
+      </c>
+      <c r="E2" s="8" t="n">
+        <v>3.4292</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>14499416.37</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>14499416.37</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L2" s="6" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="M2" s="8" t="n">
+        <v>-1522541.68</v>
+      </c>
+      <c r="N2" s="6" t="n">
+        <v>0.8565</v>
+      </c>
+      <c r="O2" s="8" t="n">
+        <v>-2261304.84</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v>0.9119</v>
+      </c>
+      <c r="Q2" s="8" t="n">
+        <v>-1137071.22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Porcelain Tile</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>26</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sq_ft</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1596610</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>3.7205</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>5940205.9</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0.1557</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>5940205.9</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L3" s="6" t="n">
+        <v>0.9229000000000001</v>
+      </c>
+      <c r="M3" s="8" t="n">
+        <v>-496430.9</v>
+      </c>
+      <c r="N3" s="6" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="O3" s="8" t="n">
+        <v>-677167.25</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v>0.8687</v>
+      </c>
+      <c r="Q3" s="8" t="n">
+        <v>-748143.97</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Laminate</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sq_ft</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1679176</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>2.5129</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>4219674.24</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>0.1106</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>4219674.24</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>0.8783</v>
+      </c>
+      <c r="M4" s="8" t="n">
+        <v>-584750.41</v>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>0.8655</v>
+      </c>
+      <c r="O4" s="8" t="n">
+        <v>-449260.72</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v>0.8622</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>-674121.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Engineered Hardwood</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sq_ft</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>485442</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>5.7737</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>2802773.48</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>2802773.48</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>16</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>0.9228</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>-234532.75</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>0.8158</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>-550894.47</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>0.9217</v>
+      </c>
+      <c r="Q5" s="8" t="n">
+        <v>-224024.53</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Natural Stone Tile</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>sq_ft</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>287147</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>8.8894</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>2552551.66</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0.0669</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>2552551.66</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>0.9484</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>-138873.89</v>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>-328419.43</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>0.8956</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>-231028.91</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ceramic Tile</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>sq_ft</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1152862</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>1.5722</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>1812485.48</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>1812485.48</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>14</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>-302387.97</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>0.8102</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>-363109.65</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>0.8451</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>-302679.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Solid Hardwood</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>sq_ft</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>205757</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>6.8571</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>1410895.63</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>1410895.63</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>0.8954</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>-164764.35</v>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>0.8378</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>-273198.11</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>0.8937</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>-136699.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Vanities &amp; Tops</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1381</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>837.3635</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>1156399</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>1156399</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="M9" s="8" t="n">
+        <v>131250</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>1.1348</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>119850</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>1.0777</v>
+      </c>
+      <c r="Q9" s="8" t="n">
+        <v>71940</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Installation Tools</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>each</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10652</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>92.4991</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>985300.3100000001</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>985300.3100000001</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>1.1094</v>
+      </c>
+      <c r="M10" s="8" t="n">
+        <v>97138.22</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>1.0109</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>10632.06</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>1.0719</v>
+      </c>
+      <c r="Q10" s="8" t="n">
+        <v>65239.31</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mosaic &amp; Decorative Tile</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sq_ft</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>52179</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>15.597</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>813835.21</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>813835.21</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="M11" s="8" t="n">
+        <v>-75586.36</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>0.9012</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>-68887.87</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>0.8563</v>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>-114286.48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Trim &amp; Moulding</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>lin_ft</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>135442</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>3.7447</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>507195.45</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>474951.68</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>32243.77</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0.9364</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>1.0058</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>2746.84</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>0.8911</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>-55072.45</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>0.9896</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>-4341.02</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Wall Tile &amp; Backsplash</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>sq_ft</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>123459</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>3.9439</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>486914.41</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>486914.41</v>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>0.8555</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>-82271.05</v>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>0.8327</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>-93267.7</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>0.8421999999999999</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>-55892</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tile Trim &amp; Edging</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>lin_ft</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>29979</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>9.2249</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>276553.62</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>276553.62</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>0.9905</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>-2646.47</v>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>0.9896</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>-2919.77</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>0.9704</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>-8440.200000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Carpet &amp; Carpet Tile</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sq_ft</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>106930</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>1.9596</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>209540.2</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>209540.2</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>-8720.610000000001</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>0.9167999999999999</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>-19010.56</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>0.8904</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>-25801.78</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Grout &amp; Caulk</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>lb</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>158842</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>1.1496</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>182603.8</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>182603.8</v>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>0.9903</v>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>-1794.38</v>
+      </c>
+      <c r="N16" s="6" t="n">
+        <v>0.9757</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>-4547.32</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>0.9575</v>
+      </c>
+      <c r="Q16" s="8" t="n">
+        <v>-8113.28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Underlayment</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sq_ft</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>275935</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>170795.09</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>151951.06</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>18844.03</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>0.9895</v>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>-1605.09</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>3042.27</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>0.9354</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>-10234.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Setting Materials</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>lb</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>249481</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0.5081</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>126755.5</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>100337.87</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>26417.63</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0.7916</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>1.0178</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>1753.53</v>
+      </c>
+      <c r="N18" s="6" t="n">
+        <v>1.0025</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>224.03</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>0.9874000000000001</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>-1175.32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>All categories</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>10779487</v>
+      </c>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n">
+        <v>38153895.34</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>38076389.92</v>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>77505.42</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>0.998</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>0.9184</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>-3384017.32</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>0.8711</v>
+      </c>
+      <c r="O19" s="9" t="n">
+        <v>-5013311.79</v>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="Q19" s="9" t="n">
+        <v>-3544873.81</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:Q18"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:W201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -20848,7 +21998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -58245,7 +59395,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
